--- a/бор өмнө.xlsx
+++ b/бор өмнө.xlsx
@@ -5,21 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SQ1\Desktop\AI_ACADEMY_BAASKA\дата цэгцлэх\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SQ1\Desktop\AI_ACADEMY_BAASKA\SubG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADBB82D-6226-4968-B134-9D106B01FAE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF8367F-D2AC-4FCE-810A-6C048BA41244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pos Order Report" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pos Order Report'!$A$3:$Y$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pos Order Report'!$A$3:$X$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -499,459 +496,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Дашборд"/>
-      <sheetName val="НҮС"/>
-      <sheetName val="ӨГС-н тэмдэглэл"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="ӨГС-н KPI"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>0107433</v>
-          </cell>
-          <cell r="C2" t="str">
-            <v>Форсига 10мг №28</v>
-          </cell>
-          <cell r="D2">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>0110058</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>Эксфорж 10мг/160мг №28</v>
-          </cell>
-          <cell r="D3">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>0102126</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>Зилт 75мг №28</v>
-          </cell>
-          <cell r="D4">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>0100998</v>
-          </cell>
-          <cell r="C5" t="str">
-            <v>Амоксиклав 625мг №15</v>
-          </cell>
-          <cell r="D5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>0102931</v>
-          </cell>
-          <cell r="C6" t="str">
-            <v>Брайнакт 500мг №30</v>
-          </cell>
-          <cell r="D6">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>0100261</v>
-          </cell>
-          <cell r="C7" t="str">
-            <v>Урсофальк 250мг №100</v>
-          </cell>
-          <cell r="D7">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>0100587</v>
-          </cell>
-          <cell r="C8" t="str">
-            <v>Терафлю №10</v>
-          </cell>
-          <cell r="D8">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>0100582</v>
-          </cell>
-          <cell r="C9" t="str">
-            <v>Ибупрофен-Денк 400мг №100</v>
-          </cell>
-          <cell r="D9">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>0109794</v>
-          </cell>
-          <cell r="C10" t="str">
-            <v>Колдвон Nose S сироп №20</v>
-          </cell>
-          <cell r="D10">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>0102912</v>
-          </cell>
-          <cell r="C11" t="str">
-            <v>Канефрон H №60</v>
-          </cell>
-          <cell r="D11">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>0112025</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>Дапаглифлозин – Фоцигли 10мг №28</v>
-          </cell>
-          <cell r="D12">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>0105173</v>
-          </cell>
-          <cell r="C13" t="str">
-            <v>Вамлосет 10мг/160мг №30 бүрхүүлтэй шахмал KRKA</v>
-          </cell>
-          <cell r="D13">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>0111906</v>
-          </cell>
-          <cell r="C14" t="str">
-            <v>КлопиКейр (Клопидогрел) 75мг №30 - таблет - DSEABI</v>
-          </cell>
-          <cell r="D14">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>0106447</v>
-          </cell>
-          <cell r="C15" t="str">
-            <v>Моксиклав 625мг №16</v>
-          </cell>
-          <cell r="D15">
-            <v>14</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>0106145</v>
-          </cell>
-          <cell r="C16" t="str">
-            <v>Этекс Цитиколин 500мг №20</v>
-          </cell>
-          <cell r="D16">
-            <v>15</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>0102477</v>
-          </cell>
-          <cell r="C17" t="str">
-            <v>Урсомон 250мг №50</v>
-          </cell>
-          <cell r="D17">
-            <v>16</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>0111893</v>
-          </cell>
-          <cell r="C18" t="str">
-            <v>ФЛУРАПИД - Flurapid №8</v>
-          </cell>
-          <cell r="D18">
-            <v>17</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>0103511</v>
-          </cell>
-          <cell r="C19" t="str">
-            <v>Гофен №50</v>
-          </cell>
-          <cell r="D19">
-            <v>18</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>0110811</v>
-          </cell>
-          <cell r="C20" t="str">
-            <v>Панпирин Кю №5</v>
-          </cell>
-          <cell r="D20">
-            <v>19</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>0531917</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>Vitos shot Бөөр хамгаалах 20мл №15</v>
-          </cell>
-          <cell r="D21">
-            <v>20</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>0111023</v>
-          </cell>
-          <cell r="C22" t="str">
-            <v>Дапа-ДМП 10мг №28 шахмал</v>
-          </cell>
-          <cell r="D22">
-            <v>21</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>0102778</v>
-          </cell>
-          <cell r="C23" t="str">
-            <v>Клопи Денк 75мг №30</v>
-          </cell>
-          <cell r="D23">
-            <v>22</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>0101478</v>
-          </cell>
-          <cell r="C24" t="str">
-            <v>Амоксиклав-Денк500/62.5№14</v>
-          </cell>
-          <cell r="D24">
-            <v>24</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>0107733</v>
-          </cell>
-          <cell r="C25" t="str">
-            <v>Урса 250мг №30</v>
-          </cell>
-          <cell r="D25">
-            <v>26</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>0107400</v>
-          </cell>
-          <cell r="C26" t="str">
-            <v>АНВИМАКС №12</v>
-          </cell>
-          <cell r="D26">
-            <v>27</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>0104832</v>
-          </cell>
-          <cell r="C27" t="str">
-            <v>Ибупрофен 400мг №10/hawon/</v>
-          </cell>
-          <cell r="D27">
-            <v>28</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>0106842</v>
-          </cell>
-          <cell r="C28" t="str">
-            <v>ТАЙЛЕНОЛ №24</v>
-          </cell>
-          <cell r="D28">
-            <v>29</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>0100485</v>
-          </cell>
-          <cell r="C29" t="str">
-            <v xml:space="preserve">Нефромон 100мл сироп </v>
-          </cell>
-          <cell r="D29">
-            <v>30</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>0111516</v>
-          </cell>
-          <cell r="C30" t="str">
-            <v>Дапапрозин 10мг №28</v>
-          </cell>
-          <cell r="D30">
-            <v>31</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>0102745</v>
-          </cell>
-          <cell r="C31" t="str">
-            <v>Плавикс 75мг №28</v>
-          </cell>
-          <cell r="D31">
-            <v>33</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>0105772</v>
-          </cell>
-          <cell r="C32" t="str">
-            <v>Бетаклав 500мг+ 125мг №14</v>
-          </cell>
-          <cell r="D32">
-            <v>34</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>0101457</v>
-          </cell>
-          <cell r="C33" t="str">
-            <v>Урса 200мг №100 капсул Палома</v>
-          </cell>
-          <cell r="D33">
-            <v>36</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>0103425</v>
-          </cell>
-          <cell r="C34" t="str">
-            <v>Грипоблок том хүн нунт/уус N12</v>
-          </cell>
-          <cell r="D34">
-            <v>37</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>0101607</v>
-          </cell>
-          <cell r="C35" t="str">
-            <v>Ибупрофен 400мг №10/протеч/</v>
-          </cell>
-          <cell r="D35">
-            <v>38</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>0109502</v>
-          </cell>
-          <cell r="C36" t="str">
-            <v xml:space="preserve">НЕЦУРЬЮ №12 </v>
-          </cell>
-          <cell r="D36">
-            <v>39</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>0103525</v>
-          </cell>
-          <cell r="C37" t="str">
-            <v>Цистон №60</v>
-          </cell>
-          <cell r="D37">
-            <v>40</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>0100782</v>
-          </cell>
-          <cell r="C38" t="str">
-            <v>Анифлу №5</v>
-          </cell>
-          <cell r="D38">
-            <v>41</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="B39" t="str">
-            <v>0101942</v>
-          </cell>
-          <cell r="C39" t="str">
-            <v>Ибупрофен 400мг №10/protech/</v>
-          </cell>
-          <cell r="D39">
-            <v>42</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>0111075</v>
-          </cell>
-          <cell r="C40" t="str">
-            <v xml:space="preserve"> Нефрос №60</v>
-          </cell>
-          <cell r="D40">
-            <v>44</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1275,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="3" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -1285,10 +829,10 @@
     <col min="5" max="16" width="12.6640625" customWidth="1"/>
     <col min="17" max="19" width="8.86328125" customWidth="1"/>
     <col min="20" max="20" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="8.86328125" customWidth="1"/>
+    <col min="21" max="24" width="8.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1338,7 +882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="23.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:24" ht="23.25" x14ac:dyDescent="0.45">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
@@ -1394,7 +938,7 @@
       <c r="W2" s="8"/>
       <c r="X2" s="8"/>
     </row>
-    <row r="3" spans="1:25" outlineLevel="3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:24" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>25</v>
       </c>
@@ -1407,16 +951,12 @@
       <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="3">
-        <f>G3/F3</f>
-        <v>41737.919506637292</v>
-      </c>
+      <c r="E3" s="3"/>
       <c r="F3" s="3">
-        <v>179.53530000000001</v>
-      </c>
-      <c r="G3" s="3">
-        <v>7493429.899999979</v>
-      </c>
+        <f>179.5353/3</f>
+        <v>59.845100000000002</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="3">
         <v>0</v>
       </c>
@@ -1451,11 +991,9 @@
         <v>0</v>
       </c>
       <c r="S3" s="3">
-        <v>179.53530000000029</v>
-      </c>
-      <c r="T3" s="3">
-        <v>7493429.899999979</v>
-      </c>
+        <v>59.845100000000002</v>
+      </c>
+      <c r="T3" s="3"/>
       <c r="U3" s="3">
         <v>0</v>
       </c>
@@ -1468,12 +1006,8 @@
       <c r="X3" s="3">
         <v>0</v>
       </c>
-      <c r="Y3">
-        <f>VLOOKUP(B3,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:24" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1486,16 +1020,11 @@
       <c r="D4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3">
-        <f t="shared" ref="E4:E26" si="0">G4/F4</f>
-        <v>157533.15555081461</v>
-      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3">
-        <v>14.999599999999999</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2362934.3199999989</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="3">
         <v>0</v>
       </c>
@@ -1530,11 +1059,9 @@
         <v>0</v>
       </c>
       <c r="S4" s="3">
-        <v>14.999599999999999</v>
-      </c>
-      <c r="T4" s="3">
-        <v>2362934.3199999989</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="T4" s="3"/>
       <c r="U4" s="3">
         <v>0</v>
       </c>
@@ -1547,12 +1074,8 @@
       <c r="X4" s="3">
         <v>0</v>
       </c>
-      <c r="Y4">
-        <f>VLOOKUP(B4,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>32</v>
       </c>
@@ -1565,16 +1088,11 @@
       <c r="D5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>43698.275030454497</v>
-      </c>
+      <c r="E5" s="3"/>
       <c r="F5" s="3">
-        <v>44.5747</v>
-      </c>
-      <c r="G5" s="3">
-        <v>1947837.5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G5" s="3"/>
       <c r="H5" s="3">
         <v>0</v>
       </c>
@@ -1609,11 +1127,9 @@
         <v>0</v>
       </c>
       <c r="S5" s="3">
-        <v>44.5747</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1947837.5</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="T5" s="3"/>
       <c r="U5" s="3">
         <v>0</v>
       </c>
@@ -1626,12 +1142,8 @@
       <c r="X5" s="3">
         <v>0</v>
       </c>
-      <c r="Y5">
-        <f>VLOOKUP(B5,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1644,16 +1156,11 @@
       <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3">
-        <f t="shared" si="0"/>
-        <v>30122.448979591834</v>
-      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3">
-        <v>27.44</v>
-      </c>
-      <c r="G6" s="3">
-        <v>826560</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G6" s="3"/>
       <c r="H6" s="3">
         <v>0</v>
       </c>
@@ -1688,11 +1195,9 @@
         <v>0</v>
       </c>
       <c r="S6" s="3">
-        <v>27.44</v>
-      </c>
-      <c r="T6" s="3">
-        <v>826560</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="T6" s="3"/>
       <c r="U6" s="3">
         <v>0</v>
       </c>
@@ -1705,12 +1210,8 @@
       <c r="X6" s="3">
         <v>0</v>
       </c>
-      <c r="Y6">
-        <f>VLOOKUP(B6,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="7" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -1723,16 +1224,11 @@
       <c r="D7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>25901.149425287356</v>
-      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3">
-        <v>43.5</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1126700</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3">
         <v>0</v>
       </c>
@@ -1767,11 +1263,9 @@
         <v>0</v>
       </c>
       <c r="S7" s="3">
-        <v>43.5</v>
-      </c>
-      <c r="T7" s="3">
-        <v>1126700</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="T7" s="3"/>
       <c r="U7" s="3">
         <v>0</v>
       </c>
@@ -1784,12 +1278,8 @@
       <c r="X7" s="3">
         <v>0</v>
       </c>
-      <c r="Y7">
-        <f>VLOOKUP(B7,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -1802,16 +1292,11 @@
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>33745.152981020066</v>
-      </c>
+      <c r="E8" s="3"/>
       <c r="F8" s="3">
-        <v>145.03760000000011</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4894316</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G8" s="3"/>
       <c r="H8" s="3">
         <v>0</v>
       </c>
@@ -1846,11 +1331,9 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>145.03760000000011</v>
-      </c>
-      <c r="T8" s="3">
-        <v>4894316</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="T8" s="3"/>
       <c r="U8" s="3">
         <v>0</v>
       </c>
@@ -1863,12 +1346,8 @@
       <c r="X8" s="3">
         <v>391</v>
       </c>
-      <c r="Y8">
-        <f>VLOOKUP(B8,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -1881,16 +1360,11 @@
       <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="3">
-        <f t="shared" si="0"/>
-        <v>10707.859914534112</v>
-      </c>
+      <c r="E9" s="3"/>
       <c r="F9" s="3">
-        <v>8.1435999999999993</v>
-      </c>
-      <c r="G9" s="3">
-        <v>87200.527999999991</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G9" s="3"/>
       <c r="H9" s="3">
         <v>0</v>
       </c>
@@ -1925,11 +1399,9 @@
         <v>0</v>
       </c>
       <c r="S9" s="3">
-        <v>8.1435999999999993</v>
-      </c>
-      <c r="T9" s="3">
-        <v>87200.527999999991</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="T9" s="3"/>
       <c r="U9" s="3">
         <v>0</v>
       </c>
@@ -1942,12 +1414,8 @@
       <c r="X9" s="3">
         <v>0</v>
       </c>
-      <c r="Y9">
-        <f>VLOOKUP(B9,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
@@ -1960,16 +1428,11 @@
       <c r="D10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>10666.666666666666</v>
-      </c>
+      <c r="E10" s="3"/>
       <c r="F10" s="3">
-        <v>0.9375</v>
-      </c>
-      <c r="G10" s="3">
-        <v>10000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3">
         <v>0</v>
       </c>
@@ -2004,11 +1467,9 @@
         <v>0</v>
       </c>
       <c r="S10" s="3">
-        <v>0.9375</v>
-      </c>
-      <c r="T10" s="3">
-        <v>10000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T10" s="3"/>
       <c r="U10" s="3">
         <v>0</v>
       </c>
@@ -2021,12 +1482,8 @@
       <c r="X10" s="3">
         <v>0</v>
       </c>
-      <c r="Y10">
-        <f>VLOOKUP(B10,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>54</v>
       </c>
@@ -2039,16 +1496,11 @@
       <c r="D11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>49222.167529938808</v>
-      </c>
+      <c r="E11" s="3"/>
       <c r="F11" s="3">
-        <v>81.608100000000007</v>
-      </c>
-      <c r="G11" s="3">
-        <v>4016927.57</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3">
         <v>0</v>
       </c>
@@ -2083,11 +1535,9 @@
         <v>0</v>
       </c>
       <c r="S11" s="3">
-        <v>81.608100000000007</v>
-      </c>
-      <c r="T11" s="3">
-        <v>4016927.57</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="T11" s="3"/>
       <c r="U11" s="3">
         <v>0</v>
       </c>
@@ -2100,12 +1550,8 @@
       <c r="X11" s="3">
         <v>0</v>
       </c>
-      <c r="Y11">
-        <f>VLOOKUP(B11,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>59</v>
       </c>
@@ -2118,16 +1564,11 @@
       <c r="D12" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="3">
-        <f t="shared" si="0"/>
-        <v>164626.2727194477</v>
-      </c>
+      <c r="E12" s="3"/>
       <c r="F12" s="3">
-        <v>59.249899999999933</v>
-      </c>
-      <c r="G12" s="3">
-        <v>9754090.195999993</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G12" s="3"/>
       <c r="H12" s="3">
         <v>0</v>
       </c>
@@ -2162,11 +1603,9 @@
         <v>0</v>
       </c>
       <c r="S12" s="3">
-        <v>59.249899999999933</v>
-      </c>
-      <c r="T12" s="3">
-        <v>9754090.195999993</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="T12" s="3"/>
       <c r="U12" s="3">
         <v>0</v>
       </c>
@@ -2179,12 +1618,8 @@
       <c r="X12" s="3">
         <v>0</v>
       </c>
-      <c r="Y12">
-        <f>VLOOKUP(B12,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>62</v>
       </c>
@@ -2197,16 +1632,11 @@
       <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="3">
-        <f t="shared" si="0"/>
-        <v>44795.956683525816</v>
-      </c>
+      <c r="E13" s="3"/>
       <c r="F13" s="3">
-        <v>125.6888999999998</v>
-      </c>
-      <c r="G13" s="3">
-        <v>5630354.5199999996</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G13" s="3"/>
       <c r="H13" s="3">
         <v>0</v>
       </c>
@@ -2241,11 +1671,9 @@
         <v>0</v>
       </c>
       <c r="S13" s="3">
-        <v>125.6888999999998</v>
-      </c>
-      <c r="T13" s="3">
-        <v>5630354.5199999996</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="T13" s="3"/>
       <c r="U13" s="3">
         <v>0</v>
       </c>
@@ -2258,12 +1686,8 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-      <c r="Y13">
-        <f>VLOOKUP(B13,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>65</v>
       </c>
@@ -2276,16 +1700,11 @@
       <c r="D14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>30000</v>
-      </c>
+      <c r="E14" s="3"/>
       <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>30000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -2320,11 +1739,9 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
-        <v>1</v>
-      </c>
-      <c r="T14" s="3">
-        <v>30000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T14" s="3"/>
       <c r="U14" s="3">
         <v>0</v>
       </c>
@@ -2337,12 +1754,8 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14">
-        <f>VLOOKUP(B14,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>69</v>
       </c>
@@ -2355,16 +1768,11 @@
       <c r="D15" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>56250</v>
-      </c>
+      <c r="E15" s="3"/>
       <c r="F15" s="3">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3">
-        <v>450000</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3">
         <v>0</v>
       </c>
@@ -2399,11 +1807,9 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
-        <v>8</v>
-      </c>
-      <c r="T15" s="3">
-        <v>450000</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="T15" s="3"/>
       <c r="U15" s="3">
         <v>0</v>
       </c>
@@ -2416,12 +1822,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15">
-        <f>VLOOKUP(B15,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>72</v>
       </c>
@@ -2434,16 +1836,11 @@
       <c r="D16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="3">
-        <f t="shared" si="0"/>
-        <v>53663.403441682582</v>
-      </c>
+      <c r="E16" s="3"/>
       <c r="F16" s="3">
-        <v>52.300000000000018</v>
-      </c>
-      <c r="G16" s="3">
-        <v>2806596</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="3">
         <v>0</v>
       </c>
@@ -2478,11 +1875,9 @@
         <v>0</v>
       </c>
       <c r="S16" s="3">
-        <v>52.300000000000018</v>
-      </c>
-      <c r="T16" s="3">
-        <v>2806596</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="T16" s="3"/>
       <c r="U16" s="3">
         <v>0</v>
       </c>
@@ -2495,12 +1890,8 @@
       <c r="X16" s="3">
         <v>7968</v>
       </c>
-      <c r="Y16">
-        <f>VLOOKUP(B16,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="17" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -2513,16 +1904,11 @@
       <c r="D17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="3">
-        <f t="shared" si="0"/>
-        <v>38340.172786177056</v>
-      </c>
+      <c r="E17" s="3"/>
       <c r="F17" s="3">
-        <v>46.300000000000061</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1775150</v>
-      </c>
+        <v>7.7166666666666766</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3">
         <v>0</v>
       </c>
@@ -2557,11 +1943,9 @@
         <v>0</v>
       </c>
       <c r="S17" s="3">
-        <v>46.300000000000061</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1775150</v>
-      </c>
+        <v>7.7166666666666766</v>
+      </c>
+      <c r="T17" s="3"/>
       <c r="U17" s="3">
         <v>0</v>
       </c>
@@ -2574,12 +1958,8 @@
       <c r="X17" s="3">
         <v>3866</v>
       </c>
-      <c r="Y17">
-        <f>VLOOKUP(B17,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="18" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>80</v>
       </c>
@@ -2592,16 +1972,11 @@
       <c r="D18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="3">
-        <f t="shared" si="0"/>
-        <v>178476.16553169189</v>
-      </c>
+      <c r="E18" s="3"/>
       <c r="F18" s="3">
-        <v>38.180000000000021</v>
-      </c>
-      <c r="G18" s="3">
-        <v>6814220</v>
-      </c>
+        <v>6.3633333333333368</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3">
         <v>0</v>
       </c>
@@ -2636,11 +2011,9 @@
         <v>0</v>
       </c>
       <c r="S18" s="3">
-        <v>38.180000000000021</v>
-      </c>
-      <c r="T18" s="3">
-        <v>6814220</v>
-      </c>
+        <v>6.3633333333333368</v>
+      </c>
+      <c r="T18" s="3"/>
       <c r="U18" s="3">
         <v>0</v>
       </c>
@@ -2653,12 +2026,8 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-      <c r="Y18">
-        <f>VLOOKUP(B18,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
@@ -2671,16 +2040,11 @@
       <c r="D19" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="3">
-        <f t="shared" si="0"/>
-        <v>17142.857142857141</v>
-      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="G19" s="3">
-        <v>60000</v>
-      </c>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="3">
         <v>0</v>
       </c>
@@ -2715,11 +2079,9 @@
         <v>0</v>
       </c>
       <c r="S19" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="T19" s="3">
-        <v>60000</v>
-      </c>
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T19" s="3"/>
       <c r="U19" s="3">
         <v>0</v>
       </c>
@@ -2732,12 +2094,8 @@
       <c r="X19" s="3">
         <v>0</v>
       </c>
-      <c r="Y19">
-        <f>VLOOKUP(B19,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="20" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>88</v>
       </c>
@@ -2750,16 +2108,11 @@
       <c r="D20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="3">
-        <f t="shared" si="0"/>
-        <v>19992.307692307684</v>
-      </c>
+      <c r="E20" s="3"/>
       <c r="F20" s="3">
-        <v>2.600000000000001</v>
-      </c>
-      <c r="G20" s="3">
-        <v>51980</v>
-      </c>
+        <v>0.43333333333333351</v>
+      </c>
+      <c r="G20" s="3"/>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -2794,11 +2147,9 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>2.600000000000001</v>
-      </c>
-      <c r="T20" s="3">
-        <v>51980</v>
-      </c>
+        <v>0.43333333333333351</v>
+      </c>
+      <c r="T20" s="3"/>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -2811,12 +2162,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20">
-        <f>VLOOKUP(B20,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
         <v>91</v>
       </c>
@@ -2829,16 +2176,11 @@
       <c r="D21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="3">
-        <f t="shared" si="0"/>
-        <v>57497.373029772127</v>
-      </c>
+      <c r="E21" s="3"/>
       <c r="F21" s="3">
-        <v>28.5500000000001</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1641550</v>
-      </c>
+        <v>4.7583333333333497</v>
+      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3">
         <v>0</v>
       </c>
@@ -2873,11 +2215,9 @@
         <v>0</v>
       </c>
       <c r="S21" s="3">
-        <v>28.5500000000001</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1641550</v>
-      </c>
+        <v>4.7583333333333497</v>
+      </c>
+      <c r="T21" s="3"/>
       <c r="U21" s="3">
         <v>0</v>
       </c>
@@ -2890,12 +2230,8 @@
       <c r="X21" s="3">
         <v>4708</v>
       </c>
-      <c r="Y21">
-        <f>VLOOKUP(B21,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>94</v>
       </c>
@@ -2908,16 +2244,11 @@
       <c r="D22" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="3">
-        <f t="shared" si="0"/>
-        <v>45604.442581726711</v>
-      </c>
+      <c r="E22" s="3"/>
       <c r="F22" s="3">
-        <v>47.720000000000027</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2176244</v>
-      </c>
+        <v>7.9533333333333376</v>
+      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3">
         <v>0</v>
       </c>
@@ -2952,11 +2283,9 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>47.720000000000027</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2176244</v>
-      </c>
+        <v>7.9533333333333376</v>
+      </c>
+      <c r="T22" s="3"/>
       <c r="U22" s="3">
         <v>0</v>
       </c>
@@ -2969,12 +2298,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22">
-        <f>VLOOKUP(B22,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
         <v>97</v>
       </c>
@@ -2987,16 +2312,11 @@
       <c r="D23" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="3">
-        <f t="shared" si="0"/>
-        <v>17388.888888888891</v>
-      </c>
+      <c r="E23" s="3"/>
       <c r="F23" s="3">
-        <v>90</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1565000</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3">
         <v>0</v>
       </c>
@@ -3031,11 +2351,9 @@
         <v>0</v>
       </c>
       <c r="S23" s="3">
-        <v>90</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1565000</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="T23" s="3"/>
       <c r="U23" s="3">
         <v>0</v>
       </c>
@@ -3048,12 +2366,8 @@
       <c r="X23" s="3">
         <v>0</v>
       </c>
-      <c r="Y23">
-        <f>VLOOKUP(B23,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>100</v>
       </c>
@@ -3066,16 +2380,11 @@
       <c r="D24" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="3">
-        <f t="shared" si="0"/>
-        <v>30954.78464236989</v>
-      </c>
+      <c r="E24" s="3"/>
       <c r="F24" s="3">
-        <v>32.838400000000021</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1016505.6000000001</v>
-      </c>
+        <v>5.4730666666666705</v>
+      </c>
+      <c r="G24" s="3"/>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -3110,11 +2419,9 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>32.838400000000021</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1016505.6000000001</v>
-      </c>
+        <v>5.4730666666666705</v>
+      </c>
+      <c r="T24" s="3"/>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -3127,12 +2434,8 @@
       <c r="X24" s="3">
         <v>456</v>
       </c>
-      <c r="Y24">
-        <f>VLOOKUP(B24,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="25" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>104</v>
       </c>
@@ -3145,16 +2448,11 @@
       <c r="D25" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="3">
-        <f t="shared" si="0"/>
-        <v>22222.222222222223</v>
-      </c>
+      <c r="E25" s="3"/>
       <c r="F25" s="3">
-        <v>2.25</v>
-      </c>
-      <c r="G25" s="3">
-        <v>50000</v>
-      </c>
+        <v>0.375</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3">
         <v>0</v>
       </c>
@@ -3189,11 +2487,9 @@
         <v>0</v>
       </c>
       <c r="S25" s="3">
-        <v>2.25</v>
-      </c>
-      <c r="T25" s="3">
-        <v>50000</v>
-      </c>
+        <v>0.375</v>
+      </c>
+      <c r="T25" s="3"/>
       <c r="U25" s="3">
         <v>0</v>
       </c>
@@ -3206,12 +2502,8 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-      <c r="Y25">
-        <f>VLOOKUP(B25,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>108</v>
       </c>
@@ -3224,16 +2516,11 @@
       <c r="D26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="3">
-        <f t="shared" si="0"/>
-        <v>49652.873563218396</v>
-      </c>
+      <c r="E26" s="3"/>
       <c r="F26" s="3">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="G26" s="3">
-        <v>863960</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3">
         <v>0</v>
       </c>
@@ -3268,11 +2555,9 @@
         <v>0</v>
       </c>
       <c r="S26" s="3">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="T26" s="3">
-        <v>863960</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="T26" s="3"/>
       <c r="U26" s="3">
         <v>0</v>
       </c>
@@ -3285,12 +2570,8 @@
       <c r="X26" s="3">
         <v>0</v>
       </c>
-      <c r="Y26">
-        <f>VLOOKUP(B26,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:24" ht="13.25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>112</v>
       </c>
@@ -3303,79 +2584,162 @@
       <c r="D27" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="3">
-        <f>G27/F27</f>
-        <v>7142.8571428571431</v>
-      </c>
+      <c r="E27" s="3"/>
       <c r="F27" s="3">
+        <v>0.46666666666666662</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
+        <v>0.46666666666666662</v>
+      </c>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="E30" s="3">
+        <v>46.300000000000061</v>
+      </c>
+      <c r="F30">
+        <f>E30/6</f>
+        <v>7.7166666666666766</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="E31" s="3">
+        <v>38.180000000000021</v>
+      </c>
+      <c r="F31">
+        <f t="shared" ref="F31:F40" si="0">E31/6</f>
+        <v>6.3633333333333368</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="E32" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="33" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E33" s="3">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>0.43333333333333351</v>
+      </c>
+    </row>
+    <row r="34" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E34" s="3">
+        <v>28.5500000000001</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>4.7583333333333497</v>
+      </c>
+    </row>
+    <row r="35" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E35" s="3">
+        <v>47.720000000000027</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>7.9533333333333376</v>
+      </c>
+    </row>
+    <row r="36" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E36" s="3">
+        <v>90</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E37" s="3">
+        <v>32.838400000000021</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>5.4730666666666705</v>
+      </c>
+    </row>
+    <row r="38" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E38" s="3">
+        <v>2.25</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="39" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E39" s="3">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="40" spans="5:6" x14ac:dyDescent="0.45">
+      <c r="E40" s="3">
         <v>2.8</v>
       </c>
-      <c r="G27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="T27" s="3">
-        <v>20000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <f>VLOOKUP(B27,[1]Sheet2!$B$2:$D$40,3,FALSE)</f>
-        <v>19</v>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>0.46666666666666662</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="V1:V2"/>
     <mergeCell ref="W1:W2"/>
     <mergeCell ref="X1:X2"/>
     <mergeCell ref="E1:E2"/>
@@ -3383,6 +2747,11 @@
     <mergeCell ref="M1:R1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:U2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="V1:V2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape"/>
